--- a/docs/TestCases_TTYTKM.xlsx
+++ b/docs/TestCases_TTYTKM.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD1375E-536E-4F4C-B32F-DB266143466A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F615B3-52DE-4E7A-B6C4-B322B0776709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4845" uniqueCount="1003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4855" uniqueCount="1013">
   <si>
     <t>TÀI LIỆU QUẢN LÝ CA KIỂM THỬ — TEST CASE MANAGEMENT</t>
   </si>
@@ -3106,12 +3106,42 @@
   <si>
     <t>98.3%</t>
   </si>
+  <si>
+    <t>File spec / Vị trí</t>
+  </si>
+  <si>
+    <t>auth.spec.ts, register.spec.ts, qna.spec.ts, smoke.spec.ts, ui.spec.ts, modal-doctor-preview.spec.ts, nav-smooth.spec.ts, screenshots.spec.ts (tests/playwright/specs/)</t>
+  </si>
+  <si>
+    <t>appointment.spec.ts, myaccount.spec.ts (tests/playwright/specs/)</t>
+  </si>
+  <si>
+    <t>letan.spec.ts, letan-flow.spec.ts, slot-mgmt.spec.ts, room-assign-preview.spec.ts, schedule-banner-room.spec.ts (TC-087..089)</t>
+  </si>
+  <si>
+    <t>bacsi.spec.ts, onduty-preview.spec.ts, workflow-preview.spec.ts, schedule-banner-room.spec.ts (TC-080..082)</t>
+  </si>
+  <si>
+    <t>admincp.spec.ts, admincp-clinic-rooms.spec.ts, schedule-banner-room.spec.ts (TC-083..086)</t>
+  </si>
+  <si>
+    <t>security.spec.ts (tests/playwright/specs/)</t>
+  </si>
+  <si>
+    <t>mobile-audit.spec.ts (tests/playwright/specs/)</t>
+  </si>
+  <si>
+    <t>tests/postman/TTYTKM_Postman_Collection.json + môi trường (newman runner)</t>
+  </si>
+  <si>
+    <t>docs/BaoCao_v4/TestCases — Manual E2E checklist (sheet "Manual E2E")</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3180,6 +3210,13 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="14">
@@ -3277,7 +3314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3333,6 +3370,19 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3340,13 +3390,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3359,11 +3402,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3713,22 +3762,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="21" x14ac:dyDescent="0.35">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27"/>
+      <c r="C2" s="29"/>
     </row>
     <row r="3" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="28"/>
+      <c r="C3" s="30"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="29"/>
+      <c r="C4" s="31"/>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
@@ -3787,10 +3836,10 @@
       </c>
     </row>
     <row r="15" spans="2:3" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="30"/>
+      <c r="C15" s="32"/>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
@@ -3833,10 +3882,10 @@
       </c>
     </row>
     <row r="22" spans="2:3" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="30"/>
+      <c r="C22" s="32"/>
     </row>
     <row r="23" spans="2:3" ht="30" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
@@ -3914,163 +3963,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="24" t="s">
         <v>834</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24" t="s">
         <v>835</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="25" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="24" t="s">
         <v>836</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26" t="s">
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26" t="s">
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26" t="s">
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
     </row>
     <row r="8" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="23">
+      <c r="A8" s="28">
         <v>10</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23">
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28">
         <v>0</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23">
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28">
         <v>2</v>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23">
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28">
         <v>0</v>
       </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23">
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28">
         <v>12</v>
       </c>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
     </row>
     <row r="9" spans="1:15" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -4120,23 +4169,23 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
     </row>
     <row r="11" spans="1:15" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -4704,12 +4753,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:O1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:O2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:O3"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:O8"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:O4"/>
     <mergeCell ref="A5:C5"/>
@@ -4719,12 +4768,12 @@
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="M7:O7"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:O1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:O2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:O3"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" sqref="K11:K22" xr:uid="{00000000-0002-0000-0900-000000000000}">
@@ -4757,7 +4806,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4765,9 +4814,10 @@
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="70.7109375" style="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="14" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>911</v>
       </c>
@@ -4792,8 +4842,11 @@
       <c r="H1" s="14" t="s">
         <v>916</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I1" s="33" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="15" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
         <v>1</v>
       </c>
@@ -4815,11 +4868,14 @@
       <c r="G2" s="17">
         <v>0</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="21" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I2" s="34" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <v>2</v>
       </c>
@@ -4841,11 +4897,14 @@
       <c r="G3" s="17">
         <v>0</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="H3" s="21" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I3" s="34" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <v>3</v>
       </c>
@@ -4867,11 +4926,14 @@
       <c r="G4" s="17">
         <v>2</v>
       </c>
-      <c r="H4" s="31" t="s">
+      <c r="H4" s="21" t="s">
         <v>1000</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I4" s="34" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>4</v>
       </c>
@@ -4893,11 +4955,14 @@
       <c r="G5" s="17">
         <v>1</v>
       </c>
-      <c r="H5" s="31" t="s">
+      <c r="H5" s="21" t="s">
         <v>1001</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I5" s="34" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <v>5</v>
       </c>
@@ -4919,11 +4984,14 @@
       <c r="G6" s="17">
         <v>0</v>
       </c>
-      <c r="H6" s="31" t="s">
+      <c r="H6" s="21" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I6" s="34" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <v>6</v>
       </c>
@@ -4945,11 +5013,14 @@
       <c r="G7" s="17">
         <v>0</v>
       </c>
-      <c r="H7" s="31" t="s">
+      <c r="H7" s="21" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="34" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>7</v>
       </c>
@@ -4971,11 +5042,14 @@
       <c r="G8" s="17">
         <v>0</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="21" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I8" s="34" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>8</v>
       </c>
@@ -4997,11 +5071,14 @@
       <c r="G9" s="17">
         <v>0</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="H9" s="21" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I9" s="34" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <v>9</v>
       </c>
@@ -5023,11 +5100,14 @@
       <c r="G10" s="17">
         <v>2</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="21" t="s">
         <v>927</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I10" s="34" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>880</v>
       </c>
@@ -5049,9 +5129,10 @@
       <c r="G11" s="20">
         <v>5</v>
       </c>
-      <c r="H11" s="32" t="s">
+      <c r="H11" s="22" t="s">
         <v>1002</v>
       </c>
+      <c r="I11" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5082,163 +5163,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="25" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26" t="s">
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26" t="s">
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26" t="s">
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
     </row>
     <row r="8" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="23">
+      <c r="A8" s="28">
         <v>138</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23">
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28">
         <v>0</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23">
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28">
         <v>0</v>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23">
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28">
         <v>0</v>
       </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23">
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28">
         <v>138</v>
       </c>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
     </row>
     <row r="9" spans="1:15" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -5288,23 +5369,23 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
     </row>
     <row r="11" spans="1:15" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -11558,23 +11639,23 @@
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A144" s="22" t="s">
+      <c r="A144" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="B144" s="22"/>
-      <c r="C144" s="22"/>
-      <c r="D144" s="22"/>
-      <c r="E144" s="22"/>
-      <c r="F144" s="22"/>
-      <c r="G144" s="22"/>
-      <c r="H144" s="22"/>
-      <c r="I144" s="22"/>
-      <c r="J144" s="22"/>
-      <c r="K144" s="22"/>
-      <c r="L144" s="22"/>
-      <c r="M144" s="22"/>
-      <c r="N144" s="22"/>
-      <c r="O144" s="22"/>
+      <c r="B144" s="27"/>
+      <c r="C144" s="27"/>
+      <c r="D144" s="27"/>
+      <c r="E144" s="27"/>
+      <c r="F144" s="27"/>
+      <c r="G144" s="27"/>
+      <c r="H144" s="27"/>
+      <c r="I144" s="27"/>
+      <c r="J144" s="27"/>
+      <c r="K144" s="27"/>
+      <c r="L144" s="27"/>
+      <c r="M144" s="27"/>
+      <c r="N144" s="27"/>
+      <c r="O144" s="27"/>
     </row>
     <row r="145" spans="1:15" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
@@ -11813,12 +11894,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:O1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:O2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:O3"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A144:O144"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:O8"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:O4"/>
     <mergeCell ref="A5:C5"/>
@@ -11828,13 +11910,12 @@
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="M7:O7"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A144:O144"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:O1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:O2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:O3"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" sqref="K145:K149 K11:K143" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -12015,163 +12096,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="24" t="s">
         <v>407</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24" t="s">
         <v>408</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="25" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26" t="s">
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26" t="s">
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26" t="s">
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
     </row>
     <row r="8" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="23">
+      <c r="A8" s="28">
         <v>10</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23">
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28">
         <v>0</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23">
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28">
         <v>0</v>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23">
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28">
         <v>0</v>
       </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23">
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28">
         <v>10</v>
       </c>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
     </row>
     <row r="9" spans="1:15" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -12221,23 +12302,23 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
     </row>
     <row r="11" spans="1:15" ht="51" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -12663,23 +12744,23 @@
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
     </row>
     <row r="21" spans="1:15" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
@@ -12730,12 +12811,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:O1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:O2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:O3"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A20:O20"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:O8"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:O4"/>
     <mergeCell ref="A5:C5"/>
@@ -12745,13 +12827,12 @@
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="M7:O7"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A20:O20"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:O1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:O2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:O3"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" sqref="K11:K19 K21" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -12804,163 +12885,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="24" t="s">
         <v>495</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24" t="s">
         <v>496</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="25" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="24" t="s">
         <v>497</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26" t="s">
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26" t="s">
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26" t="s">
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
     </row>
     <row r="8" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="23">
+      <c r="A8" s="28">
         <v>11</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23">
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28">
         <v>0</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23">
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28">
         <v>1</v>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23">
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28">
         <v>0</v>
       </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23">
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28">
         <v>12</v>
       </c>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
     </row>
     <row r="9" spans="1:15" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -13010,23 +13091,23 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
     </row>
     <row r="11" spans="1:15" ht="51" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -13405,23 +13486,23 @@
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="22"/>
-      <c r="N19" s="22"/>
-      <c r="O19" s="22"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="27"/>
     </row>
     <row r="20" spans="1:15" ht="51" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
@@ -13610,12 +13691,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:O1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:O2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:O3"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:O8"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:O4"/>
     <mergeCell ref="A5:C5"/>
@@ -13625,13 +13707,12 @@
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="M7:O7"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A19:O19"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:O1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:O2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:O3"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" sqref="K11:K18 K20" xr:uid="{00000000-0002-0000-0400-000000000000}">
@@ -13683,163 +13764,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="24" t="s">
         <v>439</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24" t="s">
         <v>440</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="25" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="24" t="s">
         <v>441</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26" t="s">
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26" t="s">
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26" t="s">
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
     </row>
     <row r="8" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="23">
+      <c r="A8" s="28">
         <v>19</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23">
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28">
         <v>0</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23">
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28">
         <v>2</v>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23">
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28">
         <v>0</v>
       </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23">
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28">
         <v>21</v>
       </c>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
     </row>
     <row r="9" spans="1:15" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -13889,23 +13970,23 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
     </row>
     <row r="11" spans="1:15" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -14472,23 +14553,23 @@
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
     </row>
     <row r="24" spans="1:15" ht="51" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -14909,12 +14990,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:O1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:O2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:O3"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:O8"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:O4"/>
     <mergeCell ref="A5:C5"/>
@@ -14924,13 +15006,12 @@
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="M7:O7"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A23:O23"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:O1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:O2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:O3"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" sqref="K11:K22 K24:K29" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -14991,163 +15072,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="24" t="s">
         <v>526</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24" t="s">
         <v>527</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="25" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="24" t="s">
         <v>528</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26" t="s">
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26" t="s">
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26" t="s">
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
     </row>
     <row r="8" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="23">
+      <c r="A8" s="28">
         <v>33</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23">
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28">
         <v>0</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23">
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28">
         <v>0</v>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23">
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28">
         <v>0</v>
       </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23">
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28">
         <v>33</v>
       </c>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
     </row>
     <row r="9" spans="1:15" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -15197,23 +15278,23 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
     </row>
     <row r="11" spans="1:15" ht="51" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -16485,23 +16566,23 @@
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="22"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="22"/>
-      <c r="N38" s="22"/>
-      <c r="O38" s="22"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="27"/>
+      <c r="K38" s="27"/>
+      <c r="L38" s="27"/>
+      <c r="M38" s="27"/>
+      <c r="N38" s="27"/>
+      <c r="O38" s="27"/>
     </row>
     <row r="39" spans="1:15" ht="51" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
@@ -16787,12 +16868,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:O1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:O2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:O3"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A38:O38"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:O8"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:O4"/>
     <mergeCell ref="A5:C5"/>
@@ -16802,13 +16884,12 @@
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="M7:O7"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A38:O38"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:O1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:O2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:O3"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" sqref="K11:K37 K39:K40" xr:uid="{00000000-0002-0000-0500-000000000000}">
@@ -16880,163 +16961,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="24" t="s">
         <v>614</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24" t="s">
         <v>615</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="25" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="24" t="s">
         <v>616</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26" t="s">
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26" t="s">
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26" t="s">
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
     </row>
     <row r="8" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="23">
+      <c r="A8" s="28">
         <v>16</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23">
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28">
         <v>0</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23">
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28">
         <v>0</v>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23">
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28">
         <v>0</v>
       </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23">
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28">
         <v>16</v>
       </c>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
     </row>
     <row r="9" spans="1:15" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -17086,23 +17167,23 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
     </row>
     <row r="11" spans="1:15" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -17858,12 +17939,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:O1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:O2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:O3"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:O8"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:O4"/>
     <mergeCell ref="A5:C5"/>
@@ -17873,12 +17954,12 @@
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="M7:O7"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:O1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:O2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:O3"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" sqref="K11:K26" xr:uid="{00000000-0002-0000-0600-000000000000}">
@@ -17937,163 +18018,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="24" t="s">
         <v>659</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24" t="s">
         <v>660</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="25" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="24" t="s">
         <v>661</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26" t="s">
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26" t="s">
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26" t="s">
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
     </row>
     <row r="8" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="23">
+      <c r="A8" s="28">
         <v>49</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23">
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28">
         <v>0</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23">
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28">
         <v>0</v>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23">
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28">
         <v>0</v>
       </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23">
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28">
         <v>49</v>
       </c>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
     </row>
     <row r="9" spans="1:15" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -18143,23 +18224,23 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
     </row>
     <row r="11" spans="1:15" ht="51" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -20466,12 +20547,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:O1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:O2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:O3"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:O8"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:O4"/>
     <mergeCell ref="A5:C5"/>
@@ -20481,12 +20562,12 @@
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="M7:O7"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:O1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:O2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:O3"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" sqref="K11:K59" xr:uid="{00000000-0002-0000-0700-000000000000}">
@@ -20578,163 +20659,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="24" t="s">
         <v>769</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24" t="s">
         <v>770</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="25" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="24" t="s">
         <v>771</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26" t="s">
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26" t="s">
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26" t="s">
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
     </row>
     <row r="8" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="23">
+      <c r="A8" s="28">
         <v>8</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23">
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28">
         <v>0</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23">
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28">
         <v>0</v>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23">
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28">
         <v>0</v>
       </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23">
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28">
         <v>8</v>
       </c>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
     </row>
     <row r="9" spans="1:15" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -20784,23 +20865,23 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
     </row>
     <row r="11" spans="1:15" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -20991,23 +21072,23 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22"/>
-      <c r="O15" s="22"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
     </row>
     <row r="16" spans="1:15" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -21199,12 +21280,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:O1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:O2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:O3"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:O8"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:O4"/>
     <mergeCell ref="A5:C5"/>
@@ -21214,13 +21296,12 @@
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="M7:O7"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A15:O15"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:O1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:O2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:O3"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" sqref="K11:K14 K16:K19" xr:uid="{00000000-0002-0000-0800-000000000000}">
